--- a/output/APAC/APAC_GC_RIR/Output/RIR_GC_APAC_NON-CORP_April 2026.xlsx
+++ b/output/APAC/APAC_GC_RIR/Output/RIR_GC_APAC_NON-CORP_April 2026.xlsx
@@ -2189,7 +2189,7 @@
       </c>
       <c r="F8" s="303" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="G8" s="304" t="n"/>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="E10" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F10" s="237" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="E11" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F11" s="237" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E12" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F12" s="237" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="E13" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F13" s="237" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="E14" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F14" s="237" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E15" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F15" s="237" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="E16" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F16" s="237" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E17" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F17" s="237" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="E18" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F18" s="237" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="E19" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F19" s="237" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="E20" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F20" s="237" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="E21" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F21" s="237" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="E22" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F22" s="237" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="E23" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F23" s="237" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E24" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F24" s="237" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="E25" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F25" s="237" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="E26" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F26" s="237" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="E27" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F27" s="237" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="E28" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F28" s="237" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="E29" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F29" s="237" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="E30" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F30" s="237" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="E31" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F31" s="237" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E32" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F32" s="237" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="E33" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F33" s="237" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="E34" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F34" s="237" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E35" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F35" s="237" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="E36" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F36" s="237" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="E37" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F37" s="237" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="E38" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F38" s="237" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E39" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F39" s="237" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="E40" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F40" s="237" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="E41" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F41" s="237" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E42" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F42" s="237" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="E43" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F43" s="237" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="E44" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F44" s="237" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="E45" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F45" s="237" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="E46" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F46" s="237" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="E47" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F47" s="237" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="E48" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F48" s="237" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="E49" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F49" s="237" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="E50" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F50" s="237" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="E51" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F51" s="237" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="E52" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F52" s="237" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="E53" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F53" s="237" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="E54" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F54" s="237" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="E55" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F55" s="237" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="E56" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F56" s="237" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="E57" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F57" s="237" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="E58" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F58" s="237" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="E59" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F59" s="237" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="E60" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F60" s="237" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="E61" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F61" s="237" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="E62" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F62" s="237" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E63" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F63" s="237" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="E64" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F64" s="237" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="E65" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F65" s="237" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="E66" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F66" s="237" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="E67" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F67" s="237" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="E68" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F68" s="237" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="E69" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F69" s="237" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="E70" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F70" s="237" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="E71" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F71" s="237" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E72" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F72" s="237" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="E73" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F73" s="237" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="E74" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F74" s="237" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="E75" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F75" s="237" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="E76" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F76" s="237" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E77" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F77" s="237" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E78" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F78" s="237" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E79" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F79" s="237" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="E80" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F80" s="237" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="E81" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F81" s="237" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="E82" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F82" s="237" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E83" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F83" s="237" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="E84" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F84" s="237" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="E85" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F85" s="237" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E86" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F86" s="237" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="E87" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F87" s="237" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="E88" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F88" s="237" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E89" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F89" s="237" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="E90" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F90" s="237" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E91" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F91" s="237" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E92" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F92" s="237" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="E93" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F93" s="237" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="E94" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F94" s="237" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="E95" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F95" s="237" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="E96" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F96" s="237" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E97" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F97" s="237" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="E98" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F98" s="237" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="E99" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F99" s="237" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="E100" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F100" s="237" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="E101" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F101" s="237" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="E102" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F102" s="237" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="E103" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F103" s="237" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E104" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F104" s="237" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="E105" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F105" s="237" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="E106" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F106" s="237" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="E107" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F107" s="237" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="E108" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F108" s="237" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="E109" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F109" s="237" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="E110" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F110" s="237" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="E111" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F111" s="237" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="E112" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F112" s="237" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="E113" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F113" s="237" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="E114" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F114" s="237" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="E115" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F115" s="237" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="E116" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F116" s="237" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="E117" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F117" s="237" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="E118" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F118" s="237" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="E119" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F119" s="237" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="E120" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F120" s="237" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="E121" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F121" s="237" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="E122" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F122" s="237" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="E123" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F123" s="237" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="E124" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F124" s="237" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="E125" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F125" s="237" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="E126" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F126" s="237" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="E127" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F127" s="237" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="E128" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F128" s="237" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="E129" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F129" s="237" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="E130" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F130" s="237" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="E131" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F131" s="237" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E132" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F132" s="237" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="E133" s="239" t="inlineStr">
         <is>
-          <t>4/24/2026</t>
+          <t>4/27/2026</t>
         </is>
       </c>
       <c r="F133" s="237" t="inlineStr">
